--- a/artfynd/A 30705-2023 artfynd.xlsx
+++ b/artfynd/A 30705-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30705-2023 artfynd.xlsx
+++ b/artfynd/A 30705-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2854,10 +2854,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115518081</v>
+        <v>115600786</v>
       </c>
       <c r="B19" t="n">
-        <v>97650</v>
+        <v>57281</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2866,40 +2866,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2908,13 +2903,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583683</v>
+        <v>583717</v>
       </c>
       <c r="R19" t="n">
-        <v>6316534</v>
+        <v>6316638</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2938,12 +2933,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2970,10 +2965,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>115600786</v>
+        <v>116456934</v>
       </c>
       <c r="B20" t="n">
-        <v>57281</v>
+        <v>97767</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2982,47 +2977,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Nyebo 1:3, Sm</t>
+          <t>Söremo (Söremo), Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583717</v>
+        <v>583689</v>
       </c>
       <c r="R20" t="n">
-        <v>6316638</v>
+        <v>6316613</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3049,12 +3039,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Knärot på nyupptaget hygge. Följ upp.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3063,133 +3058,22 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>116456934</v>
-      </c>
-      <c r="B21" t="n">
-        <v>97767</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Söremo (Söremo), Sm</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>583689</v>
-      </c>
-      <c r="R21" t="n">
-        <v>6316613</v>
-      </c>
-      <c r="S21" t="n">
-        <v>10</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Mönsterås</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Ålem</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Knärot på nyupptaget hygge. Följ upp.</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="inlineStr"/>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
